--- a/data/output/parsed/Iepf Unclaimed Dividend And Corresponding Shares Data Fy 2017 18_2017-18.xlsx
+++ b/data/output/parsed/Iepf Unclaimed Dividend And Corresponding Shares Data Fy 2017 18_2017-18.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -4932,7 +4932,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2026-03-20T23:30:23Z</t>
+          <t>2026-03-21T00:25:21Z</t>
         </is>
       </c>
     </row>

--- a/data/output/parsed/Iepf Unclaimed Dividend And Corresponding Shares Data Fy 2017 18_2017-18.xlsx
+++ b/data/output/parsed/Iepf Unclaimed Dividend And Corresponding Shares Data Fy 2017 18_2017-18.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -4932,7 +4932,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2026-03-21T00:25:21Z</t>
+          <t>2026-03-21T00:48:45Z</t>
         </is>
       </c>
     </row>
